--- a/standardDataset/standardDataset.xlsx
+++ b/standardDataset/standardDataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="19200" windowHeight="8080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>user_input</t>
   </si>
@@ -44,82 +44,365 @@
     <t>reference</t>
   </si>
   <si>
-    <t>都有谁读了《三体》</t>
-  </si>
-  <si>
-    <t>王多多：《三体》展星际博弈，水滴毁舰队、黑暗森林法则震撼，赞罗辑守护地球的勇气。
-张悦：《三体》开宇宙脑洞，叶文洁改人类命运，黑暗森林法则、水滴毁舰队，引对宇宙的敬畏与猜想。
-绘制召回率的曲线图【确保页面配色和样式美观】
-即在“用户查询”与“不相关分块”中间插入ragas方法判定的“相关分块”内容，显示出来。</t>
-  </si>
-  <si>
-    <t>张悦：
-提到《三体》中“叶文洁改写人类命运”、“黑暗森林法则”以及“水滴毁灭舰队”等情节，引发对宇宙的敬畏与猜想1。
-王多多：
-强调《三体》中“星际博弈”、“水滴毁灭舰队”和“黑暗森林法则”的震撼，特别赞赏“罗辑守护地球的勇气”1。
-（其他同学分享的书籍如《小王子》《水浒传》《窗边的小豆豆》等与《三体》无关12。）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-张悦：《三体》开宇宙脑洞，叶文洁改人类命运，黑暗森林法则、水滴毁舰队，引对宇宙的敬畏与猜想。
-王多多：《三体》展星际博弈，水滴毁舰队、黑暗森林法则震撼，赞罗辑守护地球的勇气。</t>
-  </si>
-  <si>
-    <t>根据文档内容，读过《三体》的同学包括王多多和张悦。王多多认为，《三体》展现了宏大的星际博弈，其中水滴摧毁人类舰队、黑暗森林法则等情节令人震撼，并高度赞扬了罗辑守护地球的勇气。张悦则提到，《三体》打开了自己对宇宙的脑洞，尤其是叶文洁改变了人类命运的情节，以及黑暗森林法则和水滴毁舰队的描写，引发了她对宇宙的敬畏与猜想。</t>
-  </si>
-  <si>
-    <t>读《水浒传》的同学都有什么感悟</t>
-  </si>
-  <si>
-    <t>王浩：《水浒传》好汉鲜活，武松、鲁智深等豪情足，招安悲剧唏嘘，叹皇权碾压义士。
-李陶陶：《水浒传》绘好汉群像，聚梁山求正义，招安结局唏嘘，引发对反抗与忠诚的思考。
-评估明显里的每个样本详细内容数据不做保存。</t>
-  </si>
-  <si>
-    <t>根据提供的参考资料，有两位同学分享了他们对《水浒传》的感悟：
-李陶陶：
-提到《水浒传》描绘了一群好汉的形象，他们在梁山聚义追求正义1。
-对招安的结局感到唏嘘，并引发了关于反抗与忠诚的思考1。
-王浩：
-认为《水浒传》中的好汉形象鲜活，特别提到武松、鲁智深等人的豪情2。
-对招安后的悲剧结局感到唏嘘，并感叹皇权对义士的碾压2。
-其他同学的分享与《水浒传》无关2。</t>
-  </si>
-  <si>
-    <t>李陶陶：《水浒传》绘好汉群像，聚梁山求正义，招安结局唏嘘，引发对反抗与忠诚的思考。
-王浩：《水浒传》好汉鲜活，武松、鲁智深等豪情足，招安悲剧唏嘘，叹皇权碾压义士。</t>
-  </si>
-  <si>
-    <t>读《水浒传》的同学在阅读中获得了深刻的感悟。李陶陶认为，《水浒传》生动描绘了众多好汉的群像，他们聚集在梁山追求正义，但最终的招安结局令人唏嘘，引发了对反抗与忠诚的思考。王浩则感叹书中塑造的好汉形象鲜活而豪情万丈，如武松、鲁智深等人物个性鲜明，而悲剧性的招安结局也让人深刻体会到皇权对义士的压制。这些感悟不仅体现了同学们对人物命运的共情，也展现了他们对社会制度与人性选择的深入思考。</t>
-  </si>
-  <si>
-    <t>多少人读了《百年孤独》</t>
-  </si>
-  <si>
-    <t>赵阳推荐《百年孤独》，布恩迪亚家族七代人的兴衰充满宿命感，魔幻与现实交织的写法很独特，读完满是对历史的感慨。
-刘佳分享《百年孤独》，讲述家族成员重复的命运与孤独，细腻的描写展现拉丁美洲的沧桑，让自己对 “孤独” 有了新思考。</t>
-  </si>
-  <si>
-    <t>刘佳和赵阳两人，读了《百年孤独》这本书</t>
-  </si>
-  <si>
-    <t>根据文档内容，赵阳和刘佳两位同学阅读了《百年孤独》。赵阳认为布恩迪亚家族七代人的兴衰充满了宿命感，书中魔幻与现实交织的写法非常独特，读后让人充满对历史的感慨。刘佳则通过阅读该书，对家族成员重复的命运与孤独进行了深入思考，她认为书中细腻的描写展现了拉丁美洲的历史沧桑，并让她对“孤独”这一主题有了新的理解和认识。</t>
-  </si>
-  <si>
-    <t>周凯推荐啥书籍</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-周凯推荐《时间简史》，跟着书中内容探索宇宙起源，虽有些概念难懂，但借助图解慢慢理解，感受到科学的魅力。​</t>
-  </si>
-  <si>
-    <t>周凯推荐《时间简史》</t>
-  </si>
-  <si>
-    <t>周凯推荐《时间简史》，跟着书中内容探索宇宙起源，虽有些概念难懂，但借助图解慢慢理解，感受到科学的魅力。</t>
-  </si>
-  <si>
-    <t>根据文档内容，周凯推荐了《时间简史》这本书。他提到，跟随书中的内容一起探索宇宙的起源，虽然书中有一些较为难懂的概念，但通过图解的方式，能够慢慢理解其中的原理，并深刻感受到科学的魅力。此外，其他同学如张悦和李哲也推荐了《时间简史》，他们提到这本书以通俗的方式解释了宇宙运行的规律，帮助他们逐渐理解宇宙的奥秘，并激发了对科学的兴趣。因此，周凯推荐的书籍是《时间简史》，这本书不仅具有科学深度，也能够引导读者拓宽认知边界，感受宇宙的浩瀚与神秘。</t>
+    <t>如何安装打印机驱动并连接</t>
+  </si>
+  <si>
+    <t>【打印机-3】MAC 连接打印机操作指引
+一、下载驱动包
+京瓷打印机mac系统驱动下载
+注：安装前需要先知道打印机IP地址，如下图所示：
+安装驱动
+双击驱动包
+若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包
+双击安装程序
+一路安装
+安装完成后，需要重启电脑!!!
+二、添加打印机
+进入系统偏好设置
+进入打印机与扫描仪
+添加设置
+选择IP连接，输入对应打印机IP地址，选择连接协议
+（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）
+完成添加，可以进行打印
+三、各协议解释
+Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-8】Windows系统安装京瓷打印机指引
+一、下载打印机驱动包存到电脑硬盘上
+驱动包下载地址：京瓷打印机驱动下载
+二、安装打印机
+注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）
+打印机IP地址，图示
+查询打印机型号，图示
+1、解压驱动包
+2、打开安装程序, 按步骤安装
+进入文件夹，双击Setup.exe
+接受，选择自定义安装
+以下内容请根据打印机实际型号和IP填写
+添加打印机驱动和安装升级的组件
+打印机安装完成
+三、设置打印机
+1、修改名称、设置双面打印
+打开计算机，跳至控制面板，进入硬件设备
+右击，打印机属性
+修改打印机名称
+设置双面打印
+2、打印机显示脱机时，需要设置取消SNMP
+3、添加部门id
+Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-5】MAC系统添加一体打印机部门ID
+操作前请先确认是否已安装好打印机驱动，以下步骤需要安装好驱动才能实现
+操作步骤：
+打开前往&gt;应用程序，在应用程序中找到打印机程序并双击打开
+2、选对应IP打印机
+3、添加部门ID
+Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;悦智学打印指引手册-打印机插件安装-0604
+打印机安装插件指引
+1. 打开火狐浏览器
+在地址栏输入：about:config 2. 
+3. 在搜索框搜索：security.tls.version.min 
+5. TMS点击执行安装
+警告：面临潜在的安全风险
+Firefox检测到潜在的安全威胁，因此没有继续访问localhost若您访问此网站，攻击者可能会尝试
+详细了解&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;打印机-理光、富士施乐、佳能驱动下载链接
+理光MPC5503：
+http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mpc4503/mpc4503.htm
+理光MP6054：
+http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp2554/mp2554.htm?lang=cn
+富士施乐P288：
+https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/
+富士施乐M288：
+https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/
+佳能MF244/MF249（通用）：
+https://www.canon.com.cn/supports/download/sims/list/slist?fileTypeId=23&amp;categoryId=15&amp;seriesId=77&amp;modelId=1234&amp;OSName=Windows%2010%20(x64)&amp;channel=1</t>
+  </si>
+  <si>
+    <t>根据您提供的上下文，您需要安装打印机驱动并连接打印机。由于您没有说明具体是Windows还是Mac系统，我将分别提供指引。
+**如果您使用的是Mac系统：**
+1.  **下载驱动包**：找到名为“京瓷打印机mac系统驱动下载”的链接或文件进行下载。
+2.  **安装驱动**：
+    *   双击下载好的驱动包文件。
+    *   如果桌面上找不到，可以按 `Command + 空格键`，在搜索框中输入“**Kyocera OS X 10.9+ Web build 2024.05.16**”找到并打开它。
+    *   双击安装程序，按照提示完成安装。
+    *   **重要**：安装完成后，**必须重启电脑**。
+3.  **添加打印机**：
+    *   进入 **系统偏好设置** &gt; **打印机与扫描仪**。
+    *   点击“+”号添加打印机。
+    *   选择 **IP** 方式连接。
+    *   在地址栏输入您准备好的 **打印机IP地址**，并选择协议（通常为HP Jetdirect – Socket）。
+    *   点击添加即可。如果电脑无法自动识别，请检查打印机网络连接。
+**如果您使用的是Windows系统：**
+1.  **下载驱动包**：访问“京瓷打印机驱动下载”链接，将驱动包保存到电脑上。
+2.  **安装驱动**：
+    *   解压下载好的驱动包。
+    *   进入解压后的文件夹，双击 **`Setup.exe`** 文件运行安装程序。
+    *   接受协议，选择“自定义安装”。
+    *   根据提示，输入您准备好的 **打印机IP地址** 和选择对应的 **打印机型号**。
+    *   完成安装步骤。
+3.  **设置打印机（可选）**：
+    *   安装完成后，可以到控制面板的“设备和打印机”中，右键点击打印机，进入“打印机属性”进行设置，例如修改名称、设置双面打印等。
+**重要前提和提示：**
+*   **准备工作**：在开始安装前，**您必须知道打印机的IP地址**。对于Windows系统，部分共用打印机可能还需要知道**打印机型号**和**部门密码**。
+*   **部门ID设置（仅Mac系统，且需安装驱动后）**：如果需要为打印机添加部门ID，请参考【打印机-5】。安装好驱动后，在“应用程序”中找到打印机程序，选择对应IP的打印机，然后添加部门ID。
+*   **寻求帮助**：如果在安装过程中遇到任何问题，您可以联系IT帮助台，或通过OA系统（`http://oa.zy.com`）填写IT报障单。
+请根据您的电脑操作系统选择对应的步骤进行操作。</t>
+  </si>
+  <si>
+    <t>无标准答案上下文</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【打印机-3】MAC 连接打印机操作指引
+一、下载驱动包
+京瓷打印机mac系统驱动下载
+注：安装前需要先知道打印机IP地址，如下图所示：
+安装驱动
+双击驱动包
+若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包。
+双击安装程序
+一路安装
+安装完成后，需要重启电脑!!! 
+二、添加打印机
+进入系统偏好设置
+进入打印机与扫描仪
+添加设置
+选择IP连接，输入对应打印机IP地址，选择连接协议
+（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）
+完成添加，可以进行打印
+三、各协议解释
+【打印机-8】Windows系统安装京瓷打印机指引
+一、下载打印机驱动包存到电脑硬盘上
+驱动包下载地址：京瓷打印机驱动下载
+二、安装打印机
+注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）
+打印机IP地址，图示
+查询打印机型号，图示
+1、解压驱动包
+2、打开安装程序, 按步骤安装
+进入文件夹，双击Setup.exe
+接受，选择自定义安装
+以下内容请根据打印机实际型号和IP填写
+添加打印机驱动和安装升级的组件
+打印机安装完成
+三、设置打印机
+1、修改名称、设置双面打印
+打开计算机，跳至控制面板，进入硬件设备
+右击，打印机属性
+修改打印机名称
+设置双面打印
+2、打印机显示脱机时，需要设置取消SNMP
+3、添加部门id
+</t>
+  </si>
+  <si>
+    <t>mac安装零信任</t>
+  </si>
+  <si>
+    <t>【零信任-4】mac零信任卸载手册
+卸载前确保零信任没有打开，否则无法卸载；
+退出零信任
+2.在电脑上面的菜单栏，找到前往，进入用用程序
+3.找到零信任，右键，移到废纸
+4.卸载完后，找到网络设置，找到DNS，如果有127.0.0.1，则删除保存，如果没有这一步可不管
+5.回到桌面，扎到菜单栏的实用工具
+找到终端
+6.在终端界面分别输入下面的命令
+过程将提示输入密码密码不会显示，直接输入后回车即可若密码不对，会提示错误重新输入&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ
+设备类型：
+mac
+解决方案：
+a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：
+1.10、问题：为什么我登录不了TMS、EVIP……，如下图：
+设备类型：
+Windows/mac
+解决方案：
+请先安装零信任，并扫码登录—登录后不能退出零信任
+参考下图：
+1.11、问题：安装完成不显示"零信任"（IOA冲突） 如下图：
+设备类型：
+Windows10
+解决方案：
+去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe
+1.12、问题：打开零信任没有企业微信按钮 如下图：
+设备类型：
+Windows10
+解决方案：
+重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可
+1.13、问题：安装助手完成时零信任未安装成功 如下图：
+设备类型：
+Windows10
+解决方案：
+重新安装即可
+1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ
+参考下图：
+1.5、问题：打开零信任时提示连接控制器失败，如下图：
+设备类型：
+Windows/mac
+解决方案：
+选择控制器切换124.71.208.207地址；
+b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：
+1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：
+设备类型：
+mac
+解决方案：
+a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost
+1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：
+设备类型：
+mac
+解决方案：
+a.更换Google浏览器，即可正常访问应用
+1.8、问题：启动零信任时无快捷登录方式，如下图：
+设备类型：
+Windows/mac
+解决方案：
+随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：
+1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ
+安全助手（零信任）客户端FAQ
+操作问题
+问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：
+设备类型：
+Windows/macbook
+解决方案：
+使用其他浏览器访问
+设置浏览器后重新打开进行访问应用
+（1）Google浏览器
+（2）火狐浏览器
+问题：登录零信任后当访问应用时提示无法访问此网站，如下图：
+设备类型：
+Windows/mac
+解决方案：
+ 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：
+ 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：
+问题：打开零信任扫码登陆时，提示不合法的状态，如下图
+设备类型：
+Windows/mac
+解决方案：
+a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：
+1.4、问题：安装完成不显示"零信任"（IOA冲突） 如下图：
+设备类型：
+Windows/mac
+解决方案：
+返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;mac零信任卸载手册
+（OA系统地址：http://oa.zy.com ）</t>
+  </si>
+  <si>
+    <t>根据上下文，mac安装零信任的步骤如下：
+1. **安装零信任客户端**：请先安装零信任客户端。
+2. **登录零信任**：安装完成后，扫码登录。登录后不能退出零信任。
+3. **如遇问题，参考以下解决方案**：
+   - **问题：登录不了TMS、EVIP等应用**
+     - 解决方案：确保已安装零信任并扫码登录。
+   - **问题：打开零信任时提示连接控制器失败**
+     - 解决方案：选择控制器切换为124.71.208.207地址。
+   - **问题：启动零信任时提示JavaScript错误**
+     - 解决方案：打开终端，输入命令 `sudo vi /etc/hosts`，在文件下添加 `127.0.0.1 localhost`。
+   - **问题：启动零信任时无快捷登录方式**
+     - 解决方案：随机输入一个用户名，再返回上一级，选择快捷登录方式。
+   - **问题：登录零信任后访问应用时浏览器页面提示403 forbidden**
+     - 解决方案：使用其他浏览器（如Google浏览器或火狐浏览器）访问，或设置浏览器后重新打开应用。
+   - **问题：打开零信任扫码登录时，提示不合法的状态**
+     - 解决方案：返回上一级，去掉用户名，选择快捷方式登录。
+**注意**：安装过程中如遇到其他问题，请参考上下文中的FAQ部分获取更多解决方案。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、下载安装包
+Windows系统版本
+https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe
+Macbook版本
+https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg
+2、安装完成后：
+控制器地址:124.71.208.207
+3、企业微信扫码登录后即可访问应用。
+4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink
+5、退出登陆
+企业微信扫码登录后，在不使用零信任时可选择退出登录
+6、扫码登陆时认证失败
+重新进入扫码登陆界面即可
+</t>
+  </si>
+  <si>
+    <t>电脑主机:电脑C盘满了/内存不足/磁盘空间不足，怎么清理？</t>
+  </si>
+  <si>
+    <t>【日常使用-12】C盘空间满了该如何清理
+方法一：
+win—&gt;磁盘清理
+方法二：
+ 转移微信的个人数据文件
+  微信—&gt;设置—&gt;文件管理—&gt;文件管理（微信个人数据文件就在这个文件夹里）—&gt;更改 更改至 C盘 以外的盘符）
+   更改完成后C盘就会释放出很多的空间
+方法三：
+转移企微的个人数据文件
+企微—设置—存储管理
+方法四：
+ win+r—%temp%  全选删除
+Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-7】教学一体机一键清理D盘文件指引
+在打开一体机的“此电脑”
+打开D盘
+在D盘下找到“清理D盘.bat”，双击运行清理工具
+清理工具运行中，请勿点击黑框，会停止运行
+清理结束标志“垃圾文件清理成功”，按任意键退出
+Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;非里程范围内的电脑迎检方式
+校区电脑数量及要求：
+1. 前台最好只有1 台，超过2 台的电脑必须从前台收走回避；
+2. 办公室里的办公电脑也需要按要求配置，不能出现"卓越""zy"；
+二、操作指南
+电脑数据处理
+1、清理数据
+在应检账号下删除清理桌面企业微信等其它工作图标，以及工作资料（转移到移动硬盘
+或共享盘）：检查清理磁盘无工作相关内容（例如：花名册、报名记录、共享文件夹链
+接（直接删除链接）、课件、数据分析文件、Excel 统计表格等；主要位置：浏览器下载
+保留企微或微信微信记录（可以使用企微，但必须隐蔽使用，不要自动运行/自动登录；
+目录、文档目录，各硬盘分区下的工作目录等）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;迎检前台（班辅或者班辅个辅混合的前台）及里程范围内办公室电脑处理方式
+2. Windows 操作系统账号只允许有两个：一个工作一个应检，其余账号全部禁用；
+3. 应检系统必须使用Firefox 浏览器打开，访问链接必须做成桌面快捷方式；
+校区电脑数量及要求：
+1. 前台最好只有1 台，超过2 台的电脑必须从前台收走回避；
+2. 办公室里的办公电脑也需要按要求配置；
+二、操作指南
+（一）电脑数据处理
+1、清理数据
+在应检账号下删除清理桌面企业微信等其它工作图标，以及工作资料（转移到移动硬盘
+或共享盘）：检查清理磁盘无工作相关内容（例如：花名册、报名记录、共享文件夹链
+接（直接删除链接）、课件、数据分析文件、Excel 统计表格等；主要位置：浏览器下载
+目录、文档目录，各硬盘分区下的工作目录等）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;启动提示错误：程序文件缺失 CefSharp
+一些需要注意的地方：
+如果第三步中有安全软件误报，请点击“允许”（正常情况下安全软件更新到最新是不会误报的）
+如果发现 C 盘空间已满，应该在第三步之前提前清理出一部分空间出来
+Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）</t>
+  </si>
+  <si>
+    <t>根据您提供的上下文，针对“电脑C盘满了/内存不足/磁盘空间不足”的问题，可以采取以下清理方法：
+### **方法一：使用Windows磁盘清理工具**
+1.  在Windows系统中，打开“磁盘清理”工具。
+2.  选择C盘进行扫描和清理。
+### **方法二：转移微信个人数据文件**
+1.  打开微信，进入【设置】&gt;【文件管理】。
+2.  点击“更改”，将微信个人数据文件的存储位置从C盘更改到其他盘符（如D盘、E盘等）。
+3.  更改完成后，C盘将释放大量空间。
+### **方法三：转移企业微信（企微）个人数据文件**
+1.  打开企业微信，进入【设置】&gt;【存储管理】。
+2.  在此处管理或转移个人数据文件，以释放C盘空间。
+### **方法四：清理系统临时文件**
+1.  同时按下 `Win` + `R` 键，打开“运行”对话框。
+2.  输入 `%temp%` 并回车，这会打开系统的临时文件夹。
+3.  选中该文件夹内的所有文件（`Ctrl + A`），然后将其删除。
+### **通用建议与注意事项**
+*   **提前清理空间**：在执行某些可能占用C盘空间的操作（如软件安装、更新）前，如果发现C盘空间已满，应提前按上述方法清理出一部分空间。
+*   **检查工作文件**：检查C盘的“下载”、“文档”目录以及各分区下的工作目录，将工作相关的文件（如Excel表格、课件等）转移至移动硬盘或共享盘，然后删除C盘中的原始文件。
+*   **寻求帮助**：如果在清理过程中遇到其他问题，可以联系IT帮助台，或在OA系统（地址：`http://oa.zy.com`）上填写IT报障单。
+**请注意**：上下文中的“一体机-7”指引是针对**教学一体机D盘**的清理，与您询问的C盘问题不直接相关。而“迎检方式”部分主要涉及为应对检查而进行的数据清理和系统配置，其中关于清理工作文件的部分建议可以作为释放磁盘空间的参考。您的问题应主要参考【日常使用-12】和“启动提示错误”中的相关方法。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【日常使用-12】C盘空间满了该如何清理
+方法一：
+win—&gt;磁盘清理
+方法二：
+      转移微信的个人数据文件
+     微信——&gt;设置——&gt;文件管理——&gt;文件管理（微信个人数据文件就在这个文件夹里）——&gt;更改   更改至 C盘 以外的盘符）
+      更改完成后 C盘 就会释放出很多的空间
+方法三：
+转移企微的个人数据文件
+企微—设置—存储管理
+方法四：
+     win+r—%temp%  全选删除
+</t>
   </si>
 </sst>
 </file>
@@ -132,16 +415,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+  <fonts count="20">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -293,7 +568,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,12 +577,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -493,27 +762,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -632,52 +886,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,87 +949,77 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1119,17 +1366,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="33.25" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="46.5" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="68.625" style="1" customWidth="1"/>
+    <col min="1" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1142,29 +1385,29 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="228" customHeight="1" spans="1:5">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="120" customHeight="1" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1174,48 +1417,31 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" ht="114" customHeight="1" spans="1:5">
-      <c r="A4" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="124" customHeight="1" spans="1:5">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/standardDataset/standardDataset.xlsx
+++ b/standardDataset/standardDataset.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>user_input</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>reference</t>
+  </si>
+  <si>
+    <t>测试</t>
   </si>
   <si>
     <t>如何安装打印机驱动并连接</t>
@@ -1366,13 +1369,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1388,56 +1391,68 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:5">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
